--- a/data/base/Backlog_9.xlsx
+++ b/data/base/Backlog_9.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE47C842-A3A1-443D-9621-C8067AD788C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB0397AF-F1EC-4E8D-9025-473F5CCC7F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="27">
   <si>
     <t>Status</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>Lourival Silva</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -683,7 +686,7 @@
         <v>46090</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>21</v>
@@ -788,7 +791,7 @@
         <v>46090</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>21</v>
@@ -823,7 +826,7 @@
         <v>46090</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>21</v>
@@ -858,7 +861,7 @@
         <v>46090</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>21</v>
@@ -928,7 +931,7 @@
         <v>46090</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>21</v>
@@ -963,7 +966,7 @@
         <v>46090</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>21</v>
@@ -1079,7 +1082,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
         <v>2026</v>
@@ -1094,7 +1097,7 @@
         <v>46094</v>
       </c>
       <c r="G2" s="7">
-        <v>9411</v>
+        <v>12219</v>
       </c>
       <c r="H2" s="12">
         <v>46023</v>
@@ -1103,7 +1106,7 @@
         <v>46090</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>5</v>
@@ -1114,7 +1117,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2">
         <v>2026</v>
@@ -1129,7 +1132,7 @@
         <v>46094</v>
       </c>
       <c r="G3" s="7">
-        <v>10016</v>
+        <v>12244</v>
       </c>
       <c r="H3" s="12">
         <v>46054</v>
@@ -1138,7 +1141,7 @@
         <v>46090</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>5</v>
@@ -1149,7 +1152,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2">
         <v>2026</v>
@@ -1164,7 +1167,7 @@
         <v>46094</v>
       </c>
       <c r="G4" s="7">
-        <v>11479</v>
+        <v>12309</v>
       </c>
       <c r="H4" s="12">
         <v>46054</v>
@@ -1173,7 +1176,7 @@
         <v>46090</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>5</v>
@@ -1184,7 +1187,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>2026</v>
@@ -1199,7 +1202,7 @@
         <v>46094</v>
       </c>
       <c r="G5" s="7">
-        <v>11586</v>
+        <v>12314</v>
       </c>
       <c r="H5" s="12">
         <v>46054</v>
@@ -1208,7 +1211,7 @@
         <v>46090</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>5</v>
@@ -1219,7 +1222,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2">
         <v>2026</v>
@@ -1234,7 +1237,7 @@
         <v>46094</v>
       </c>
       <c r="G6" s="7">
-        <v>11970</v>
+        <v>12315</v>
       </c>
       <c r="H6" s="12">
         <v>46082</v>
@@ -1243,7 +1246,7 @@
         <v>46090</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>5</v>
@@ -1254,7 +1257,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2">
         <v>2026</v>
@@ -1269,7 +1272,7 @@
         <v>46094</v>
       </c>
       <c r="G7" s="7">
-        <v>12129</v>
+        <v>12320</v>
       </c>
       <c r="H7" s="12">
         <v>46082</v>
@@ -1289,7 +1292,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2">
         <v>2026</v>
@@ -1304,7 +1307,7 @@
         <v>46094</v>
       </c>
       <c r="G8" s="7">
-        <v>12209</v>
+        <v>12338</v>
       </c>
       <c r="H8" s="12">
         <v>46082</v>
@@ -1339,7 +1342,7 @@
         <v>46094</v>
       </c>
       <c r="G9" s="7">
-        <v>12219</v>
+        <v>12374</v>
       </c>
       <c r="H9" s="12">
         <v>46082</v>
@@ -1359,7 +1362,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2">
         <v>2026</v>
@@ -1374,7 +1377,7 @@
         <v>46094</v>
       </c>
       <c r="G10" s="7">
-        <v>12244</v>
+        <v>9411</v>
       </c>
       <c r="H10" s="12">
         <v>46082</v>
@@ -1394,7 +1397,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2">
         <v>2026</v>
@@ -1409,7 +1412,7 @@
         <v>46094</v>
       </c>
       <c r="G11" s="7">
-        <v>12249</v>
+        <v>10016</v>
       </c>
       <c r="H11" s="12">
         <v>46082</v>
@@ -1429,7 +1432,7 @@
         <v>24</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2">
         <v>2026</v>
@@ -1444,7 +1447,7 @@
         <v>46094</v>
       </c>
       <c r="G12" s="7">
-        <v>12275</v>
+        <v>11479</v>
       </c>
       <c r="H12" s="12">
         <v>46082</v>
@@ -1453,7 +1456,7 @@
         <v>46090</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>5</v>
@@ -1464,7 +1467,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2">
         <v>2026</v>
@@ -1479,7 +1482,7 @@
         <v>46094</v>
       </c>
       <c r="G13" s="7">
-        <v>12309</v>
+        <v>11970</v>
       </c>
       <c r="H13" s="12">
         <v>46082</v>
@@ -1488,7 +1491,7 @@
         <v>46090</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>5</v>
@@ -1499,7 +1502,7 @@
         <v>24</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2">
         <v>2026</v>
@@ -1514,7 +1517,7 @@
         <v>46094</v>
       </c>
       <c r="G14" s="7">
-        <v>12314</v>
+        <v>12209</v>
       </c>
       <c r="H14" s="12">
         <v>46082</v>
@@ -1523,7 +1526,7 @@
         <v>46090</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>5</v>
@@ -1534,7 +1537,7 @@
         <v>24</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2">
         <v>2026</v>
@@ -1549,7 +1552,7 @@
         <v>46094</v>
       </c>
       <c r="G15" s="7">
-        <v>12315</v>
+        <v>12275</v>
       </c>
       <c r="H15" s="12">
         <v>46082</v>
@@ -1558,7 +1561,7 @@
         <v>46090</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>5</v>
@@ -1569,7 +1572,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
         <v>2026</v>
@@ -1584,7 +1587,7 @@
         <v>46094</v>
       </c>
       <c r="G16" s="7">
-        <v>12320</v>
+        <v>12129</v>
       </c>
       <c r="H16" s="12">
         <v>46082</v>
@@ -1593,7 +1596,7 @@
         <v>46090</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>5</v>
@@ -1604,7 +1607,7 @@
         <v>24</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2">
         <v>2026</v>
@@ -1619,7 +1622,7 @@
         <v>46094</v>
       </c>
       <c r="G17" s="7">
-        <v>12333</v>
+        <v>11586</v>
       </c>
       <c r="H17" s="12">
         <v>46082</v>
@@ -1639,7 +1642,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2">
         <v>2026</v>
@@ -1654,7 +1657,7 @@
         <v>46094</v>
       </c>
       <c r="G18" s="7">
-        <v>12338</v>
+        <v>12249</v>
       </c>
       <c r="H18" s="12">
         <v>46082</v>
@@ -1663,7 +1666,7 @@
         <v>46090</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>5</v>
@@ -1689,7 +1692,7 @@
         <v>46094</v>
       </c>
       <c r="G19" s="7">
-        <v>12339</v>
+        <v>12333</v>
       </c>
       <c r="H19" s="12">
         <v>46082</v>
@@ -1698,7 +1701,7 @@
         <v>46090</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>5</v>
@@ -1724,7 +1727,7 @@
         <v>46094</v>
       </c>
       <c r="G20" s="7">
-        <v>12349</v>
+        <v>12339</v>
       </c>
       <c r="H20" s="12">
         <v>46082</v>
@@ -1733,7 +1736,7 @@
         <v>46090</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>5</v>
@@ -1759,7 +1762,7 @@
         <v>46094</v>
       </c>
       <c r="G21" s="7">
-        <v>12351</v>
+        <v>12349</v>
       </c>
       <c r="H21" s="12">
         <v>46082</v>
@@ -1768,7 +1771,7 @@
         <v>46090</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>5</v>
@@ -1794,7 +1797,7 @@
         <v>46094</v>
       </c>
       <c r="G22" s="7">
-        <v>12354</v>
+        <v>12351</v>
       </c>
       <c r="H22" s="12">
         <v>46082</v>
@@ -1803,7 +1806,7 @@
         <v>46090</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>5</v>
@@ -1814,7 +1817,7 @@
         <v>24</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C23" s="2">
         <v>2026</v>
@@ -1829,7 +1832,7 @@
         <v>46094</v>
       </c>
       <c r="G23" s="7">
-        <v>12374</v>
+        <v>12354</v>
       </c>
       <c r="H23" s="12">
         <v>46082</v>
@@ -1838,7 +1841,7 @@
         <v>46090</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>5</v>
@@ -1873,7 +1876,7 @@
         <v>46090</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>5</v>
@@ -1890,7 +1893,7 @@
     <row r="27" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G28">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G24">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
